--- a/SimWheeling/BOM.xlsx
+++ b/SimWheeling/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chengfeng Yang\Desktop\project\sim racing\SimWheeling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A4DEB8-0E1D-4ACC-86D0-0DD01F841AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C032DED-2342-4759-AF95-BED5E038FBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t>物料</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>旋钮固定螺丝</t>
+  </si>
+  <si>
+    <t>羽毛球手胶</t>
   </si>
 </sst>
 </file>
@@ -1110,6 +1113,14 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O37" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C38" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1142,7 +1153,7 @@
       </c>
       <c r="O40" s="1">
         <f>SUM(O3:O38)</f>
-        <v>421.07000000000005</v>
+        <v>431.07000000000005</v>
       </c>
     </row>
   </sheetData>
